--- a/14-automacao_tarefas/files/receita.xlsx
+++ b/14-automacao_tarefas/files/receita.xlsx
@@ -127,7 +127,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -184,6 +184,22 @@
       </c>
       <c r="B7" s="1" t="n">
         <v>95000</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B8" s="0" t="n">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B9" s="0" t="n">
+        <v>80000</v>
       </c>
     </row>
   </sheetData>
